--- a/output/satyam_test_2.xlsx
+++ b/output/satyam_test_2.xlsx
@@ -8035,7 +8035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -8120,11 +8120,13 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C:52.0, AS:52.0, AD:52.0</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
+          <t>C:49.0, AS:49.0, AD:49.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Mismatch</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8140,7 +8142,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -8148,11 +8150,13 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C:467948.0, AS:467948.0, AD:467948.0</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
+          <t>C:440951.0, AS:440951.0, AD:440951.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Mismatch</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -8425,6 +8429,422 @@
       <c r="F14" t="inlineStr">
         <is>
           <t>Count of sales that still lack a valid sale date</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>G. Total Sales</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>52</v>
+      </c>
+      <c r="D15" t="n">
+        <v>52</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Total Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>G. Attributed Sales</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>49</v>
+      </c>
+      <c r="D16" t="n">
+        <v>49</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Attributed Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>G. Unattributed Sales</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Unattributed Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>G. Total Revenue</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>467948</v>
+      </c>
+      <c r="D18" t="n">
+        <v>467948</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>G. Attributed Revenue</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>440951</v>
+      </c>
+      <c r="D19" t="n">
+        <v>440951</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Attributed Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>G. Unattributed Revenue</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>26997</v>
+      </c>
+      <c r="D20" t="n">
+        <v>26997</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Unattributed Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>G. Raw Meta Spend</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>456047.55</v>
+      </c>
+      <c r="D21" t="n">
+        <v>282120.59</v>
+      </c>
+      <c r="E21" t="n">
+        <v>173926.96</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Raw Meta Spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>G. Attributed Spend</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>282120.59</v>
+      </c>
+      <c r="D22" t="n">
+        <v>282120.59</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Attributed Spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>G. Unallocated Spend</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>173926.96</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>173926.96</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Unallocated Spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>G. Profit</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>158830.41</v>
+      </c>
+      <c r="D24" t="n">
+        <v>158830.41</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>G. ROAS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Golden Report verification for ROAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>G. ROI %</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Golden Report verification for ROI %</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>G. CAC</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5757.56</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5757.56</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Golden Report verification for CAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>INV. Revenue Formula</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Attributed + Unattributed = Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>INV. Spend Formula</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Attributed + Unallocated = Raw Spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>INV. Profit Formula</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Attributed Revenue - Attributed Spend = Profit</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -14529,7 +14949,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>foremost leads | cbo | 11th august 2026</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Primary</t>
@@ -14547,7 +14971,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -14555,10 +14979,10 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>26997</v>
+        <v>8999</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>26997</v>
+        <v>8999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -14584,7 +15008,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026</t>
+          <t>foremost leads | cbo | 14th august</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -14641,7 +15065,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august</t>
+          <t>--</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -14653,26 +15077,22 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -14691,7 +15111,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -15667,7 +16087,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fml-cprg-cbo-p1 [12-12-25] cprg</t>
+          <t>chatgpt.com</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -15679,20 +16099,16 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G26" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>0</v>
@@ -16457,7 +16873,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>fml-cbo-test – copy</t>
+          <t>fml-cprg-cbo-p1 [12-12-25] cprg</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -16514,7 +16930,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>fml-cbo-test – copy</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -16526,16 +16942,20 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>7</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
-      <c r="G41" s="4" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H41" s="2" t="n">
         <v>0</v>
@@ -16567,7 +16987,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>fml-am-abo-campaign</t>
+          <t>fml-c1-broad - travel interests – copy</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -17023,7 +17443,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>fml-abo-c2</t>
+          <t>fml-am-abo-campaign</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -17080,7 +17500,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>fml-cbo-test</t>
+          <t>fml-abo-c2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -17479,7 +17899,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>chatgpt.com</t>
+          <t>fml-c1-broad - travel interests</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -17491,16 +17911,20 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
-      <c r="G58" s="4" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H58" s="2" t="n">
         <v>0</v>
@@ -17532,7 +17956,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>fml-c1-broad - travel interests</t>
+          <t>fml-c1-wn</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -17589,7 +18013,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>fml-c1-broad - travel interests – copy</t>
+          <t>fml-cbo-test</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -17646,7 +18070,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>fml-c1-wn</t>
+          <t>fml-c1-wn [03-01-26]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -17703,7 +18127,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>fml-c1-wn [03-01-26]</t>
+          <t>fml-cbo-p2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -17760,7 +18184,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>fml-cbo-p2</t>
+          <t>fml-cbo-c1 [03-11-25]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -17817,7 +18241,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>fml-cbo-c1 [03-11-25]</t>
+          <t>fml-cbo-5</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -17874,7 +18298,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>fml-cbo-5</t>
+          <t>fml-cbo-4</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -17931,7 +18355,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>fml-cbo-4</t>
+          <t>fml-cbo-3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -17988,7 +18412,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>fml-cbo-3</t>
+          <t>fml-cbo 2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -18045,7 +18469,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>fml-cbo 2</t>
+          <t>fml-cbo 1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -18102,7 +18526,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>fml-cbo 1</t>
+          <t>fml-c3-wn- cbo [05-01-26]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -18159,7 +18583,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>fml-c3-wn- cbo [05-01-26]</t>
+          <t>fml-c3-wn [09-02-26 ]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -18216,7 +18640,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>fml-c3-wn [09-02-26 ]</t>
+          <t>fml-c3-abo-002 [09-12-25]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -18273,7 +18697,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>fml-c3-abo-002 [09-12-25]</t>
+          <t>fml-c3-002</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -18330,7 +18754,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>fml-c3-002</t>
+          <t>fml-c2-wn</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -18387,7 +18811,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>fml-c2-wn</t>
+          <t>fml-c2-cbo-002</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -18444,7 +18868,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>fml-c2-cbo-002</t>
+          <t>fml-c2-broad - travel</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -18501,7 +18925,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>fml-c2-broad - travel</t>
+          <t>fml-c2-002 [08-12-25]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -18558,7 +18982,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>fml-c2-002 [08-12-25]</t>
+          <t>{{campaign.name}}</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -18570,20 +18994,16 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G77" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>0</v>
@@ -18607,59 +19027,6 @@
         </is>
       </c>
       <c r="M77" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>{{campaign.name}}</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" t="n">
-        <v>14</v>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -18676,7 +19043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -18764,7 +19131,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &gt; </t>
+          <t>-- &gt; --</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -18776,26 +19143,22 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>26997</v>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -18814,14 +19177,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-- &gt; --</t>
+          <t>chatgpt.com &gt; --</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -18833,7 +19196,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
@@ -18874,7 +19237,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>chatgpt.com &gt; --</t>
+          <t>fml-p1-002 &gt; coding languages – copy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -18927,7 +19290,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fml-p1-002 &gt; coding languages – copy</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -18936,51 +19299,45 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>118171.8760061444</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>380</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>310.978621068801</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>3.421052631578948</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>116987</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>9404.320714285714</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>1.08741482157467</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>8.741482157467049</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -18989,31 +19346,31 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>118171.8760061444</v>
+        <v>22068.2419047619</v>
       </c>
       <c r="D6" t="n">
-        <v>380</v>
+        <v>70</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>310.978621068801</v>
+        <v>315.2605986394558</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.421052631578948</v>
+        <v>7.142857142857142</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>116987</v>
+        <v>44995</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>9404.320714285714</v>
+        <v>3617.046428571426</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>1.08741482157467</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.741482157467049</v>
+        <v>8.741482157467043</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>8275.590714285714</v>
@@ -19027,7 +19384,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -19036,31 +19393,31 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>22068.2419047619</v>
+        <v>56950.30168970814</v>
       </c>
       <c r="D7" t="n">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>315.2605986394558</v>
+        <v>296.6161546338965</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7.142857142857142</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>44995</v>
+        <v>71992</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>3617.046428571426</v>
+        <v>5787.274285714288</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>1.08741482157467</v>
+        <v>1.087414821574671</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.741482157467043</v>
+        <v>8.741482157467054</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>8275.590714285714</v>
@@ -19074,7 +19431,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -19083,25 +19440,25 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>56950.30168970814</v>
+        <v>34526.12039938556</v>
       </c>
       <c r="D8" t="n">
-        <v>192</v>
+        <v>133</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>296.6161546338965</v>
+        <v>259.5948902209441</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.166666666666666</v>
+        <v>1.503759398496241</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>71992</v>
+        <v>17998</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>5787.274285714288</v>
+        <v>1446.818571428572</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>1.087414821574671</v>
@@ -19121,7 +19478,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -19130,45 +19487,51 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>34526.12039938556</v>
+        <v>851.4197635135137</v>
       </c>
       <c r="D9" t="n">
-        <v>133</v>
+        <v>3</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>259.5948902209441</v>
+        <v>283.8065878378379</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.503759398496241</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>17998</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>1446.818571428572</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>1.087414821574671</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>8.741482157467054</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>8275.590714285714</v>
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -19177,40 +19540,34 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>851.4197635135137</v>
+        <v>49552.63023648649</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>220</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>283.8065878378379</v>
+        <v>225.2392283476659</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0</v>
+        <v>2.272727272727273</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>44995</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>-5409.050000000003</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.8926862027952118</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>-10.73137972047882</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>10080.81</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -19221,7 +19578,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -19230,45 +19587,51 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>49552.63023648649</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>220</v>
+        <v>122</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>225.2392283476659</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.272727272727273</v>
+        <v>2.459016393442623</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>-5409.050000000003</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>0.8926862027952118</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>-10.73137972047882</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>10080.81</v>
+        <v>26997</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>26997</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -19280,22 +19643,22 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.459016393442623</v>
+        <v>4.320987654320987</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>26997</v>
+        <v>62993</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>26997</v>
+        <v>62993</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -19321,7 +19684,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -19333,22 +19696,26 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>162</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>4.320987654320987</v>
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>62993</v>
+        <v>8999</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>62993</v>
+        <v>8999</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -19374,7 +19741,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55</t>
+          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -19431,7 +19798,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 |</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -19443,26 +19810,22 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -19481,14 +19844,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 |</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 |</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -19500,7 +19863,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
@@ -19541,7 +19904,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 |</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 |</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -19553,7 +19916,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
@@ -19594,7 +19957,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 |</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 |</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -19606,7 +19969,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
@@ -19647,7 +20010,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 |</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -19659,22 +20022,22 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0</v>
+        <v>2.395209580838324</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>35996</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>35996</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -19693,14 +20056,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open</t>
+          <t>{{campaign.name}} &gt; {{adset.name}}</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -19712,22 +20075,22 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>167</v>
+        <v>14</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.395209580838324</v>
+        <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>35996</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>35996</v>
+        <v>0</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -19745,59 +20108,6 @@
         </is>
       </c>
       <c r="M20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>{{campaign.name}} &gt; {{adset.name}}</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>14</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -19814,7 +20124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -19902,7 +20212,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &gt;  &gt; </t>
+          <t>-- &gt; -- &gt; --</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -19914,26 +20224,22 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>26997</v>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -19952,14 +20258,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-- &gt; -- &gt; --</t>
+          <t>chatgpt.com &gt; -- &gt; --</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -19971,7 +20277,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
@@ -20012,7 +20318,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>chatgpt.com &gt; -- &gt; --</t>
+          <t>fml-p1-002 &gt; coding languages – copy &gt; abhishekpal-ad 2 hook 6-1;1 ratio-311025-006</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -20065,7 +20371,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fml-p1-002 &gt; coding languages – copy &gt; abhishekpal-ad 2 hook 6-1;1 ratio-311025-006</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience &gt; split screen &lt;&gt; germany is actively hiring international talent right now &gt;</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -20074,51 +20380,45 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>118171.8760061444</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>380</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>310.978621068801</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>3.421052631578948</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>116987</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>9404.320714285714</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>1.08741482157467</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>8.741482157467049</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience &gt; split screen &lt;&gt; germany is actively hiring international talent right now &gt;</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy &gt; image ad &lt;&gt; sticky note &lt;&gt; join this masterclass, dubai's tech sector is growing fast and sponsoring visas now</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -20127,31 +20427,31 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>118171.8760061444</v>
+        <v>22068.2419047619</v>
       </c>
       <c r="D6" t="n">
-        <v>380</v>
+        <v>70</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>310.978621068801</v>
+        <v>315.2605986394558</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.421052631578948</v>
+        <v>7.142857142857142</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>116987</v>
+        <v>44995</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>9404.320714285714</v>
+        <v>3617.046428571426</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>1.08741482157467</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.741482157467049</v>
+        <v>8.741482157467043</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>8275.590714285714</v>
@@ -20165,7 +20465,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy &gt; image ad &lt;&gt; sticky note &lt;&gt; join this masterclass, dubai's tech sector is growing fast and sponsoring visas now</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -20174,19 +20474,19 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>22068.2419047619</v>
+        <v>28593.79730670763</v>
       </c>
       <c r="D7" t="n">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>315.2605986394558</v>
+        <v>257.6017775379066</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7.142857142857142</v>
+        <v>4.504504504504505</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>44995</v>
@@ -20212,7 +20512,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; if you want a it job abroad in 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -20221,45 +20521,51 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>28593.79730670763</v>
+        <v>949.1716948284691</v>
       </c>
       <c r="D8" t="n">
-        <v>111</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>257.6017775379066</v>
+        <v>135.595956404067</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.504504504504505</v>
+        <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>3617.046428571426</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>1.08741482157467</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>8.741482157467043</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>8275.590714285714</v>
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; if you want a it job abroad in 2026</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; what if i get rejected my english not that good &lt;&gt; navy blue blazer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -20268,51 +20574,45 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>949.1716948284691</v>
+        <v>27407.33268817205</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>135.595956404067</v>
+        <v>370.3693606509736</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0</v>
+        <v>4.054054054054054</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>26997</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>2170.227857142858</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.087414821574671</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>8.741482157467054</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; what if i get rejected my english not that good &lt;&gt; navy blue blazer</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; laptop screen | if you're an it professional in india &amp; looking to get</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -20321,45 +20621,51 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>27407.33268817205</v>
+        <v>118.6464618535586</v>
       </c>
       <c r="D10" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>370.3693606509736</v>
+        <v>118.6464618535586</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4.054054054054054</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>2170.227857142858</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>1.087414821574671</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>8.741482157467054</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>8275.590714285714</v>
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; laptop screen | if you're an it professional in india &amp; looking to get</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -20368,51 +20674,45 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>118.6464618535586</v>
+        <v>34407.47393753201</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>118.6464618535586</v>
+        <v>260.6626813449394</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0</v>
+        <v>1.515151515151515</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>17998</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>1446.818571428572</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>1.087414821574671</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>8.741482157467054</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -20421,45 +20721,51 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>34407.47393753201</v>
+        <v>851.4197635135137</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>260.6626813449394</v>
+        <v>283.8065878378379</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.515151515151515</v>
+        <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>17998</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>1446.818571428572</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>1.087414821574671</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>8.741482157467054</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>8275.590714285714</v>
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -20468,40 +20774,34 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>851.4197635135137</v>
+        <v>49552.63023648649</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>220</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>283.8065878378379</v>
+        <v>225.2392283476659</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0</v>
+        <v>2.272727272727273</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>44995</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>-5409.050000000003</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.8926862027952118</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>-10.73137972047882</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>10080.81</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -20512,7 +20812,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; --</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -20521,34 +20821,40 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>49552.63023648649</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>220</v>
+        <v>1</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>225.2392283476659</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.272727272727273</v>
+        <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I14" s="7" t="n">
-        <v>-5409.050000000003</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>0.8926862027952118</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>-10.73137972047882</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>10080.81</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -20559,7 +20865,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; --</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09&lt;attention it professionals if you are an it engineer&gt; – copy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -20571,22 +20877,22 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0</v>
+        <v>2.479338842975207</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>26997</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>26997</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -20605,14 +20911,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09&lt;attention it professionals if you are an it engineer&gt; – copy</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremostleads-gs-13-09&lt;do you know which countries are actively sponsoring visas&gt; – copy 2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -20624,22 +20930,22 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.479338842975207</v>
+        <v>4.320987654320987</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>26997</v>
+        <v>62993</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>26997</v>
+        <v>62993</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -20665,7 +20971,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremostleads-gs-13-09&lt;do you know which countries are actively sponsoring visas&gt; – copy 2</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -20677,22 +20983,26 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>162</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>4.320987654320987</v>
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>62993</v>
+        <v>8999</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>62993</v>
+        <v>8999</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -20718,7 +21028,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 7</t>
+          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -20775,7 +21085,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 2</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | dubai's tech sector is growing fast and sponsoring visas now</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -20787,26 +21097,22 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -20825,14 +21131,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | dubai's tech sector is growing fast and sponsoring visas now</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | stop applying to places that were never going to sponsor you. find out who actually does</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -20844,7 +21150,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
@@ -20885,7 +21191,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | stop applying to places that were never going to sponsor you. find out who actually does</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 | &gt; image ads | whiteboard | pick the right country for your experience. not just what's trending</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -20897,7 +21203,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -20938,7 +21244,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 | &gt; image ads | whiteboard | pick the right country for your experience. not just what's trending</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | sticky notes | germany is short on tech workers and hiring from india right now</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -20950,7 +21256,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
@@ -20991,7 +21297,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | sticky notes | germany is short on tech workers and hiring from india right now</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | whiteboard | know what dutch companies look for before you apply</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -21003,7 +21309,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
@@ -21044,7 +21350,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | whiteboard | know what dutch companies look for before you apply</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 | &gt; image ads | ignored vs shortlisted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -21056,7 +21362,7 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>0</v>
@@ -21097,7 +21403,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 | &gt; image ads | ignored vs shortlisted</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504(1).mp4&gt;</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -21109,22 +21415,26 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>27</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>26997</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>26997</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -21143,14 +21453,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504(1).mp4&gt;</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt;</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -21162,26 +21472,22 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>167</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0.5988023952095809</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>26997</v>
+        <v>8999</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>26997</v>
+        <v>8999</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -21207,7 +21513,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt;</t>
+          <t>{{campaign.name}} &gt; {{adset.name}} &gt; {{ad.name}}</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -21219,22 +21525,22 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>167</v>
+        <v>14</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.5988023952095809</v>
+        <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I27" s="5" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -21252,59 +21558,6 @@
         </is>
       </c>
       <c r="M27" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>{{campaign.name}} &gt; {{adset.name}} &gt; {{ad.name}}</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>14</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -21321,14 +21574,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Raw Meta Spend</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>282120.59</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Attributed Spend</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>282120.59</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Unallocated Spend</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21341,14 +21634,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Funnel Stage</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Total Leads</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Paid Leads</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Unpaid Leads</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/satyam_test_2.xlsx
+++ b/output/satyam_test_2.xlsx
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3795</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="14">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3712</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="15">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>83</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>97.8129117259552</v>
+        <v>98.36888331242159</v>
       </c>
     </row>
     <row r="17">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.187088274044796</v>
+        <v>1.631116687578419</v>
       </c>
     </row>
     <row r="18">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3715</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="19">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -1584,7 +1584,7 @@
   <dimension ref="A1:AB71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
@@ -1757,8 +1757,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>46242</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1854,8 +1856,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>46242</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1951,8 +1955,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>46242</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -2048,8 +2054,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>46242</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -2145,8 +2153,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>46242</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -2242,8 +2252,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>46242</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2339,8 +2351,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>46242</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2436,8 +2450,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>46242</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2533,8 +2549,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>46242</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2630,8 +2648,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>46242</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2727,8 +2747,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>46242</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2824,8 +2846,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>46242</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2921,8 +2945,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>46242</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -3018,8 +3044,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>46242</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3115,8 +3143,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>46242</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3212,8 +3242,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46242</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3309,8 +3341,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>46242</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3406,8 +3440,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>46242</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -3503,8 +3539,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>46242</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -3600,8 +3638,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>46242</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -3697,8 +3737,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>46242</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3794,8 +3836,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>46242</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3896,8 +3940,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>46242</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3993,8 +4039,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>46242</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -4090,8 +4138,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>46242</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -4192,8 +4242,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>46242</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -4289,8 +4341,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>46242</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -4386,8 +4440,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>46242</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -4483,8 +4539,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>46242</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -4580,8 +4638,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>46242</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4677,8 +4737,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>46242</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4774,8 +4836,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>46242</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4871,8 +4935,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>46242</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4968,8 +5034,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>46242</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -5065,8 +5133,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>46242</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -5162,8 +5232,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>46242</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -5259,8 +5331,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>46242</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -5356,8 +5430,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>46242</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -5453,8 +5529,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
-        <v>46242</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5550,8 +5628,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>46242</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5647,8 +5727,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
-        <v>46242</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5744,8 +5826,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>46242</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -5841,8 +5925,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
-        <v>46242</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5938,8 +6024,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
-        <v>46242</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -6035,8 +6123,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
-        <v>46242</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -6132,8 +6222,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
-        <v>46242</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -6229,8 +6321,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
-        <v>46242</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -6326,8 +6420,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
-        <v>46242</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -6423,8 +6519,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
-        <v>46242</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -6520,8 +6618,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
-        <v>46242</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -6617,8 +6717,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
-        <v>46242</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -6714,8 +6816,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
-        <v>46242</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -6811,8 +6915,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
-        <v>46242</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6908,8 +7014,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
-        <v>46242</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -7005,8 +7113,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
-        <v>46242</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -7102,8 +7212,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
-        <v>46242</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -7199,8 +7311,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
-        <v>46242</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -7296,8 +7410,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
-        <v>46242</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -7393,8 +7509,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
-        <v>46242</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -7490,8 +7608,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
-        <v>46242</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -7587,8 +7707,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
-        <v>46242</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -7684,8 +7806,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
-        <v>46242</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -7781,8 +7905,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
-        <v>46242</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -7878,8 +8004,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
-        <v>46242</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -7975,8 +8103,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
-        <v>46242</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -8072,8 +8202,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
-        <v>46242</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -8169,8 +8301,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
-        <v>46242</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -8266,8 +8400,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
-        <v>46242</v>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -8363,8 +8499,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
-        <v>46242</v>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -8460,8 +8598,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
-        <v>46242</v>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -8810,10 +8950,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3795</v>
+        <v>1594</v>
       </c>
       <c r="D9" t="n">
-        <v>3795</v>
+        <v>1594</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15298,14 +15438,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -15398,16 +15538,16 @@
         <v>231716.54</v>
       </c>
       <c r="D2" t="n">
-        <v>1992</v>
+        <v>803</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>288.5635616438356</v>
       </c>
       <c r="F2" t="n">
         <v>28</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>1.405622489959839</v>
+        <v>3.486924034869241</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>251972</v>
@@ -15445,7 +15585,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>732</v>
+        <v>300</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
@@ -15454,7 +15594,7 @@
         <v>9</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1.229508196721312</v>
+        <v>3</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>80991</v>
@@ -15498,16 +15638,16 @@
         <v>50404.05</v>
       </c>
       <c r="D4" t="n">
-        <v>598</v>
+        <v>227</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>222.0442731277533</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.8361204013377926</v>
+        <v>2.202643171806168</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>44995</v>
@@ -15545,7 +15685,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>243</v>
+        <v>171</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -15554,7 +15694,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1.646090534979424</v>
+        <v>2.339181286549707</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>35996</v>
@@ -15598,7 +15738,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
@@ -15607,7 +15747,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.448275862068965</v>
+        <v>12.5</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>8999</v>
@@ -15651,16 +15791,20 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>1.666666666666667</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H7" s="2" t="n">
         <v>8999</v>
@@ -15704,16 +15848,20 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>5.555555555555555</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H8" s="2" t="n">
         <v>8999</v>
@@ -15745,7 +15893,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fml-test-campaign</t>
+          <t>fml-test-1nov</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -15802,7 +15950,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>foremost</t>
+          <t>fml-test-instant-form</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -15814,16 +15962,20 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="4" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H10" s="2" t="n">
         <v>0</v>
@@ -15855,7 +16007,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fml-test-instant-form</t>
+          <t>fml-test-campaign-all</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -15912,7 +16064,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fml-test-campaign-all</t>
+          <t>fml-test-campaign</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -15969,7 +16121,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fml-test-1nov</t>
+          <t>fml-test-002</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -16083,7 +16235,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fml-test-002</t>
+          <t>fml-test campaign</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -16140,7 +16292,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fml-test campaign</t>
+          <t>fml-target test</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -16197,7 +16349,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fml-target test</t>
+          <t>fml-retargeting - showup</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -16254,7 +16406,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fml-retargeting - showup</t>
+          <t>fml-p2-002 – copy</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -16311,7 +16463,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fml-p2-002 – copy</t>
+          <t>fml-p2-002</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -16368,7 +16520,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fml-p2-002</t>
+          <t>fml-p1-broad - job &amp; career</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -16425,7 +16577,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fml-p1-broad - job &amp; career</t>
+          <t>fml-p1-002 – copy _ cprg</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -16710,7 +16862,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fml-p1-002</t>
+          <t>chatgpt.com</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -16889,7 +17041,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>0</v>
@@ -17443,7 +17595,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>fml-p1-002 – copy _ cprg</t>
+          <t>fml-p1-002</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17455,20 +17607,16 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G39" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>0</v>
@@ -17557,7 +17705,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>chatgpt.com</t>
+          <t>fml-cbo-test – copy</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -17569,16 +17717,20 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
-      <c r="G41" s="4" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H41" s="2" t="n">
         <v>0</v>
@@ -17610,7 +17762,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>fml-am1-abo</t>
+          <t>fml-c1-broad - travel interests – copy</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -17667,7 +17819,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>fml-c1-broad - travel interests</t>
+          <t>fml-c1-broad - job interests</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -17724,7 +17876,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>fml-c1-broad - job interests</t>
+          <t>fml-c1-broad - job &amp; career</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -17781,7 +17933,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>fml-c1-broad - job &amp; career</t>
+          <t>fml-c1-broad - engaged shoppers</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -17838,7 +17990,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>fml-c1-broad - engaged shoppers</t>
+          <t>fml-c1-broad - corporates</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -17895,7 +18047,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>fml-c1-broad - corporates</t>
+          <t>fml-c1-002</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -17952,7 +18104,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>fml-c1-002</t>
+          <t>fml-bdc-acc-test</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -18009,7 +18161,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>fml-bdc-acc-test</t>
+          <t>fml-am1-abo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -18123,7 +18275,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>fml-cbo-test – copy</t>
+          <t>fml-abo-c2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -18180,7 +18332,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>fml-abo-c2</t>
+          <t>fml-abo-c1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -18237,7 +18389,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>fml-abo-c1</t>
+          <t>fml-5a-3c-002</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -18294,7 +18446,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>fml-5a-3c-002</t>
+          <t>fml- cbo- s</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -18351,7 +18503,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>fml- cbo- s</t>
+          <t>fml- am2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -18408,7 +18560,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>fml- am2</t>
+          <t>fml p1 engaged shoppers + travel adventure [01-12-25]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -18465,7 +18617,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>fml p1 engaged shoppers + travel adventure [01-12-25]</t>
+          <t>fml - p1 - travel interest</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -18522,7 +18674,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>fml - p1 - travel interest</t>
+          <t>fml-c1-broad - travel interests</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -18579,7 +18731,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>fml-c1-broad - travel interests – copy</t>
+          <t>fml-c1-wn</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -18636,7 +18788,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>fml-c1-wn</t>
+          <t>fml-cbo-test</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -18750,7 +18902,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>fml-c2-002 [08-12-25]</t>
+          <t>fml-cbo-p2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -18807,7 +18959,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>fml-cbo-test</t>
+          <t>fml-cbo-c1 [03-11-25]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -18864,7 +19016,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>fml-cbo-p2</t>
+          <t>fml-cbo-5</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -18921,7 +19073,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>fml-cbo-c1 [03-11-25]</t>
+          <t>fml-cbo-4</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -18978,7 +19130,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>fml-cbo-5</t>
+          <t>fml-cbo-3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -19035,7 +19187,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>fml-cbo-4</t>
+          <t>fml-cbo 2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -19092,7 +19244,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>fml-cbo-3</t>
+          <t>fml-cbo 1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -19149,7 +19301,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>fml-cbo 2</t>
+          <t>fml-c3-wn- cbo [05-01-26]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -19206,7 +19358,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>fml-cbo 1</t>
+          <t>fml-c3-wn [09-02-26 ]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -19263,7 +19415,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>fml-c3-wn- cbo [05-01-26]</t>
+          <t>fml-c3-abo-002 [09-12-25]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -19320,7 +19472,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>fml-c3-wn [09-02-26 ]</t>
+          <t>fml-c3-002</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -19377,7 +19529,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>fml-c3-abo-002 [09-12-25]</t>
+          <t>fml-c2-wn</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -19434,7 +19586,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>fml-c3-002</t>
+          <t>fml-c2-cbo-002</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -19491,7 +19643,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>fml-c2-wn</t>
+          <t>fml-c2-broad - travel</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -19548,7 +19700,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>fml-c2-cbo-002</t>
+          <t>fml-c2-002 [08-12-25]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -19605,7 +19757,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>fml-c2-broad - travel</t>
+          <t>{{campaign.name}}</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -19617,20 +19769,16 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G77" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>0</v>
@@ -19654,59 +19802,6 @@
         </is>
       </c>
       <c r="M77" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>{{campaign.name}}</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" t="n">
-        <v>51</v>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -19723,7 +19818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -19823,7 +19918,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -19832,7 +19927,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>3.448275862068965</v>
+        <v>12.5</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>8999</v>
@@ -19970,7 +20065,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>foremost &gt; --</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -19979,40 +20074,34 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>118068.4177208835</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>392</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>301.1949431655192</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>3.316326530612245</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>116987</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>-1081.417720883546</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>0.9908407536769058</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>-0.9159246323094147</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>9082.185978529504</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -20023,7 +20112,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -20032,45 +20121,45 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>118068.4177208835</v>
+        <v>22334.1243373494</v>
       </c>
       <c r="D6" t="n">
-        <v>1015</v>
+        <v>74</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>301.8124910452622</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.280788177339901</v>
+        <v>6.756756756756757</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>116987</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>-1081.417720883546</v>
+        <v>44995</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>22660.8756626506</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.9908407536769058</v>
+        <v>2.014630138185215</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.9159246323094147</v>
+        <v>101.4630138185215</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>9082.185978529504</v>
+        <v>4466.82486746988</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -20079,34 +20168,34 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>22334.1243373494</v>
+        <v>56765.89935742972</v>
       </c>
       <c r="D7" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>285.255775665476</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.604166666666667</v>
+        <v>4.020100502512562</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>44995</v>
+        <v>71992</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>22660.8756626506</v>
+        <v>15226.10064257028</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>2.014630138185215</v>
+        <v>1.268226185349381</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>101.4630138185215</v>
+        <v>26.82261853493815</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>4466.82486746988</v>
+        <v>7095.737419678715</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -20117,7 +20206,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -20126,45 +20215,45 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>56765.89935742972</v>
+        <v>34548.09858433735</v>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
+        <v>138</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>250.3485404662127</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.639344262295082</v>
+        <v>1.449275362318841</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>71992</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>15226.10064257028</v>
+        <v>17998</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>-16550.09858433735</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>1.268226185349381</v>
+        <v>0.5209548640155709</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>26.82261853493815</v>
+        <v>-47.90451359844292</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>7095.737419678715</v>
+        <v>17274.04929216867</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -20173,34 +20262,36 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>34548.09858433735</v>
+        <v>842.8770903010034</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>3</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>280.9590301003345</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.6734006734006733</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>17998</v>
+        <v>0</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>-16550.09858433735</v>
+        <v>-842.8770903010034</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.5209548640155709</v>
+        <v>0</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-47.90451359844292</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>17274.04929216867</v>
+        <v>-100</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -20211,7 +20302,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -20220,36 +20311,34 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>842.8770903010034</v>
+        <v>49561.172909699</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>224</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>84.28770903010033</v>
+        <v>221.2552362040134</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0</v>
+        <v>2.232142857142857</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
+        <v>44995</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>-842.8770903010034</v>
+        <v>-4566.172909699002</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0</v>
+        <v>0.9078679409379875</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>-9.213205906201249</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>9912.2345819398</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -20260,7 +20349,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -20269,45 +20358,51 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>49561.172909699</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>588</v>
+        <v>128</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.8503401360544218</v>
+        <v>2.34375</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>-4566.172909699002</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>0.9078679409379875</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>-9.213205906201249</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>9912.2345819398</v>
+        <v>26997</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>26997</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -20319,22 +20414,22 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>288</v>
+        <v>172</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.041666666666667</v>
+        <v>3.488372093023256</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>26997</v>
+        <v>53994</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>26997</v>
+        <v>53994</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -20360,7 +20455,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -20372,22 +20467,26 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>444</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>1.351351351351351</v>
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>53994</v>
+        <v>8999</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>53994</v>
+        <v>8999</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -20413,7 +20512,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; data science | 30 -55</t>
+          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -20425,22 +20524,26 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -20459,14 +20562,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 |</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -20478,7 +20581,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
@@ -20519,7 +20622,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 |</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -20531,22 +20634,22 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -20565,14 +20668,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 |</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -20584,22 +20687,22 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>9.090909090909092</v>
+        <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -20618,14 +20721,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; core it professionals | 25 - 55</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 |</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -20637,7 +20740,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
@@ -20678,7 +20781,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 |</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -20690,22 +20793,22 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>171</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0</v>
+        <v>2.339181286549707</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>35996</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>35996</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -20724,14 +20827,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 |</t>
+          <t>{{campaign.name}} &gt; {{adset.name}}</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -20743,7 +20846,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
@@ -20776,218 +20879,6 @@
         </is>
       </c>
       <c r="M20" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 |</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>8</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 |</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>27</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>243</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>1.646090534979424</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>35996</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>35996</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>{{campaign.name}} &gt; {{adset.name}}</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>51</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -21004,7 +20895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -21104,7 +20995,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -21113,7 +21004,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>3.448275862068965</v>
+        <v>12.5</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>8999</v>
@@ -21251,7 +21142,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>foremost &gt; -- &gt; --</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience &gt; split screen &lt;&gt; germany is actively hiring international talent right now &gt;</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -21260,40 +21151,34 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>118068.4177208835</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>392</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>301.1949431655192</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>3.316326530612245</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>116987</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>-1081.417720883546</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>0.9908407536769058</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>-0.9159246323094147</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>9082.185978529504</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -21304,7 +21189,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience &gt; split screen &lt;&gt; germany is actively hiring international talent right now &gt;</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy &gt; image ad &lt;&gt; sticky note &lt;&gt; join this masterclass, dubai's tech sector is growing fast and sponsoring visas now</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -21313,45 +21198,45 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>118068.4177208835</v>
+        <v>22334.1243373494</v>
       </c>
       <c r="D6" t="n">
-        <v>1015</v>
+        <v>74</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>301.8124910452622</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.280788177339901</v>
+        <v>6.756756756756757</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>116987</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>-1081.417720883546</v>
+        <v>44995</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>22660.8756626506</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.9908407536769058</v>
+        <v>2.014630138185215</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.9159246323094147</v>
+        <v>101.4630138185215</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>9082.185978529504</v>
+        <v>4466.82486746988</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy &gt; image ad &lt;&gt; sticky note &lt;&gt; join this masterclass, dubai's tech sector is growing fast and sponsoring visas now</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -21360,34 +21245,34 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>22334.1243373494</v>
+        <v>28150.3025502008</v>
       </c>
       <c r="D7" t="n">
-        <v>192</v>
+        <v>112</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>251.3419870553643</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.604166666666667</v>
+        <v>4.464285714285714</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>44995</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>22660.8756626506</v>
+        <v>16844.6974497992</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>2.014630138185215</v>
+        <v>1.598384241865956</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>101.4630138185215</v>
+        <v>59.83842418659561</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>4466.82486746988</v>
+        <v>5630.060510040161</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -21398,7 +21283,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; if you want a it job abroad in 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -21407,45 +21292,47 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>28150.3025502008</v>
+        <v>1163.235642570281</v>
       </c>
       <c r="D8" t="n">
-        <v>242</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>129.2484047300312</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.066115702479339</v>
+        <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>16844.6974497992</v>
+        <v>0</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>-1163.235642570281</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>1.598384241865956</v>
+        <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>59.83842418659561</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>5630.060510040161</v>
+        <v>-100</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; if you want a it job abroad in 2026</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; what if i get rejected my english not that good &lt;&gt; navy blue blazer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -21454,36 +21341,34 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1163.235642570281</v>
+        <v>27452.36116465864</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>351.9533482648543</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0</v>
+        <v>3.846153846153846</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0</v>
+        <v>26997</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>-1163.235642570281</v>
+        <v>-455.361164658636</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0</v>
+        <v>0.9834126776226136</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>-1.658732237738642</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>9150.787054886212</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -21494,7 +21379,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; what if i get rejected my english not that good &lt;&gt; navy blue blazer</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; laptop screen | if you're an it professional in india &amp; looking to get</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -21503,34 +21388,36 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>27452.36116465864</v>
+        <v>116.3235642570281</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>116.3235642570281</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.271186440677966</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>26997</v>
+        <v>0</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>-455.361164658636</v>
+        <v>-116.3235642570281</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.9834126776226136</v>
+        <v>0</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.658732237738642</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>9150.787054886212</v>
+        <v>-100</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -21541,7 +21428,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; laptop screen | if you're an it professional in india &amp; looking to get</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -21550,36 +21437,34 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>34431.77502008032</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>251.3268249640899</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0</v>
+        <v>1.45985401459854</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
+        <v>17998</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>-116.3235642570281</v>
+        <v>-16433.77502008032</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0</v>
+        <v>0.5227148466642721</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>-47.72851533357279</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>17215.88751004016</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -21590,7 +21475,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -21599,34 +21484,36 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>34431.77502008032</v>
+        <v>842.8770903010034</v>
       </c>
       <c r="D12" t="n">
-        <v>296</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>280.9590301003345</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.6756756756756757</v>
+        <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>17998</v>
+        <v>0</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>-16433.77502008032</v>
+        <v>-842.8770903010034</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.5227148466642721</v>
+        <v>0</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-47.72851533357279</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>17215.88751004016</v>
+        <v>-100</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -21637,7 +21524,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -21646,36 +21533,34 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>842.8770903010034</v>
+        <v>49561.172909699</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>224</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>84.28770903010033</v>
+        <v>221.2552362040134</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0</v>
+        <v>2.232142857142857</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0</v>
+        <v>44995</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>-842.8770903010034</v>
+        <v>-4566.172909699002</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0</v>
+        <v>0.9078679409379875</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>-9.213205906201249</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>9912.2345819398</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -21686,7 +21571,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; --</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -21695,34 +21580,40 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>49561.172909699</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>588</v>
+        <v>1</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.8503401360544218</v>
+        <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I14" s="7" t="n">
-        <v>-4566.172909699002</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>0.9078679409379875</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>-9.213205906201249</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>9912.2345819398</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -21733,7 +21624,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; --</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09&lt;attention it professionals if you are an it engineer&gt; – copy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -21745,22 +21636,22 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0</v>
+        <v>2.362204724409449</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>26997</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>26997</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -21779,14 +21670,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt; – copy 2</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremostleads-gs-13-09&lt;do you know which countries are actively sponsoring visas&gt; – copy 2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -21798,22 +21689,22 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>172</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0</v>
+        <v>3.488372093023256</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>53994</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>53994</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -21832,14 +21723,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09&lt;attention it professionals if you are an it engineer&gt; – copy</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -21851,22 +21742,26 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>286</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>1.048951048951049</v>
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>26997</v>
+        <v>8999</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>26997</v>
+        <v>8999</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -21892,7 +21787,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremost leads-13-09&lt;do you know which countries are hiring&gt; – copy 2</t>
+          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -21904,22 +21799,26 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -21938,14 +21837,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremostleads-gs-13-09&lt;do you know which countries are actively sponsoring visas&gt; – copy 2</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | dubai's tech sector is growing fast and sponsoring visas now</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -21957,22 +21856,22 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>443</v>
+        <v>1</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.354401805869075</v>
+        <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>53994</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>53994</v>
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -21991,14 +21890,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; data science | 30 -55 &gt; split ad 10</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | stop applying to places that were never going to sponsor you. find out who actually does</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -22051,7 +21950,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; data science | 30 -55 &gt; split ad 4</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 | &gt; image ads | whiteboard | pick the right country for your experience. not just what's trending</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -22063,7 +21962,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -22104,7 +22003,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55 &gt; split ad 1</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | sticky notes | germany is short on tech workers and hiring from india right now</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -22157,7 +22056,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55 &gt; split ad 2</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | whiteboard | know what dutch companies look for before you apply</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -22169,7 +22068,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
@@ -22210,7 +22109,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55 &gt; split ad 3</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 | &gt; image ads | ignored vs shortlisted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -22222,7 +22121,7 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>0</v>
@@ -22263,7 +22162,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 5</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504(1).mp4&gt;</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -22275,22 +22174,26 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>26997</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>26997</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -22309,14 +22212,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 6</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt;</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -22328,22 +22231,22 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>171</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0</v>
+        <v>0.5847953216374269</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -22362,14 +22265,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 7</t>
+          <t>{{campaign.name}} &gt; {{adset.name}} &gt; {{ad.name}}</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -22381,22 +22284,22 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I27" s="5" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -22414,642 +22317,6 @@
         </is>
       </c>
       <c r="M27" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 1</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 2</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 14th august &gt; core it professionals | 25 - 55 &gt; abhishek pal 5</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>7</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | dubai's tech sector is growing fast and sponsoring visas now</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | stop applying to places that were never going to sponsor you. find out who actually does</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 | &gt; image ads | whiteboard | pick the right country for your experience. not just what's trending</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>29</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | sticky notes | germany is short on tech workers and hiring from india right now</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>7</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | whiteboard | know what dutch companies look for before you apply</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 | &gt; image ads | ignored vs shortlisted</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>27</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504(1).mp4&gt;</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>72</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>3</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>4.166666666666666</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I37" s="5" t="n">
-        <v>26997</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt;</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
-        <v>171</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>0.5847953216374269</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>{{campaign.name}} &gt; {{adset.name}} &gt; {{ad.name}}</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
-        <v>51</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -23066,7 +22333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -23166,7 +22433,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -23175,7 +22442,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>3.448275862068965</v>
+        <v>12.5</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>8999</v>
@@ -23313,7 +22580,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>foremost &gt; --</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_desktop_feed</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -23322,13 +22589,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>465.2942570281124</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>232.6471285140562</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -23339,18 +22606,14 @@
       <c r="H5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I5" s="7" t="n">
+        <v>-465.2942570281124</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>-100</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -23366,7 +22629,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_desktop_feed</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_instream_video</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -23378,10 +22641,10 @@
         <v>465.2942570281124</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>232.6471285140562</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -23415,7 +22678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_instream_video</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_mobile_feed</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -23424,13 +22687,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>465.2942570281124</v>
+        <v>3955.001184738956</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>247.1875740461847</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -23442,7 +22705,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>-465.2942570281124</v>
+        <v>-3955.001184738956</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>0</v>
@@ -23464,7 +22727,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_mobile_feed</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_mobile_reels</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -23473,47 +22736,45 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>3955.001184738956</v>
+        <v>12446.62137550201</v>
       </c>
       <c r="D8" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>234.8419127453209</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0</v>
+        <v>3.773584905660377</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>-3955.001184738956</v>
+        <v>17998</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>5551.378624497991</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0</v>
+        <v>1.446014902921725</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>44.60149029217246</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>6223.310687751004</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_mobile_reels</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_stories</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -23522,45 +22783,47 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>12446.62137550201</v>
+        <v>697.9413855421687</v>
       </c>
       <c r="D9" t="n">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>697.9413855421687</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.869158878504673</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>17998</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>5551.378624497991</v>
+        <v>0</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>-697.9413855421687</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>1.446014902921725</v>
+        <v>0</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>44.60149029217246</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>6223.310687751004</v>
+        <v>-100</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_stories</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; instagram_feed</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -23569,47 +22832,45 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>697.9413855421687</v>
+        <v>25940.15482931727</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>308.8113670156818</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0</v>
+        <v>3.571428571428571</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>-697.9413855421687</v>
+        <v>26997</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1056.845170682729</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0</v>
+        <v>1.040741667797923</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>4.074166779792288</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>8646.718276439091</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; instagram_feed</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; instagram_reels</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -23618,34 +22879,34 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>25940.15482931727</v>
+        <v>170297.6980722892</v>
       </c>
       <c r="D11" t="n">
-        <v>223</v>
+        <v>596</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>285.7343927387402</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.345291479820628</v>
+        <v>3.691275167785235</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>26997</v>
+        <v>197978</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>1056.845170682729</v>
+        <v>27680.30192771083</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>1.040741667797923</v>
+        <v>1.1625406699036</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4.074166779792288</v>
+        <v>16.25406699035996</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>8646.718276439091</v>
+        <v>7740.804457831327</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -23656,7 +22917,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; instagram_reels</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; instagram_stories</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -23665,45 +22926,45 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>170297.6980722892</v>
+        <v>14540.44553212851</v>
       </c>
       <c r="D12" t="n">
-        <v>1464</v>
+        <v>41</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>354.6450129787443</v>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.502732240437158</v>
+        <v>2.439024390243902</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>197978</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>27680.30192771083</v>
+        <v>8999</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>-5541.445532128515</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>1.1625406699036</v>
+        <v>0.6188943784504981</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>16.25406699035996</v>
+        <v>-38.11056215495018</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>7740.804457831327</v>
+        <v>14540.44553212851</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; instagram_stories</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; others</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -23712,34 +22973,36 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>14540.44553212851</v>
+        <v>2675.441977911647</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>334.4302472389558</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>8999</v>
+        <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>-5541.445532128515</v>
+        <v>-2675.441977911647</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.6188943784504981</v>
+        <v>0</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-38.11056215495018</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>14540.44553212851</v>
+        <v>-100</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -23750,7 +23013,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; others</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; threads_feed</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -23759,25 +23022,29 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>2675.441977911647</v>
+        <v>232.6471285140562</v>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="4" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>-2675.441977911647</v>
+        <v>-232.6471285140562</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>0</v>
@@ -23799,7 +23066,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; threads_feed</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; facebook_instream_video</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -23808,13 +23075,13 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>232.6471285140562</v>
+        <v>84.28770903010034</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>84.28770903010034</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -23826,7 +23093,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>-232.6471285140562</v>
+        <v>-84.28770903010034</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>0</v>
@@ -23848,7 +23115,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; facebook_instream_video</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; facebook_mobile_feed</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -23857,13 +23124,13 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>674.3016722408028</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>112.3836120401338</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -23875,7 +23142,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>-84.28770903010034</v>
+        <v>-674.3016722408028</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>0</v>
@@ -23897,7 +23164,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; facebook_mobile_feed</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; facebook_mobile_reels</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -23906,47 +23173,45 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>674.3016722408028</v>
+        <v>2444.34356187291</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>152.7714726170569</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>-674.3016722408028</v>
+        <v>8999</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>6554.65643812709</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0</v>
+        <v>3.681561029458873</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>268.1561029458874</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>2444.34356187291</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; facebook_mobile_reels</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; facebook_stories</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -23955,45 +23220,47 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>2444.34356187291</v>
+        <v>84.28770903010034</v>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>84.28770903010034</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.448275862068965</v>
+        <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>6554.65643812709</v>
+        <v>0</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>-84.28770903010034</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>3.681561029458873</v>
+        <v>0</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>268.1561029458874</v>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>2444.34356187291</v>
+        <v>-100</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; facebook_stories</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; instagram_feed</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -24002,13 +23269,13 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>2612.918979933111</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>290.324331103679</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -24020,7 +23287,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>-84.28770903010034</v>
+        <v>-2612.918979933111</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>0</v>
@@ -24042,7 +23309,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; instagram_feed</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; instagram_reels</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -24051,36 +23318,34 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2612.918979933111</v>
+        <v>43576.74556856188</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>231.7911998327759</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0</v>
+        <v>2.127659574468085</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0</v>
+        <v>35996</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>-2612.918979933111</v>
+        <v>-7580.745568561877</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0</v>
+        <v>0.8260369040952211</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>-17.39630959047788</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>10894.18639214047</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -24091,7 +23356,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; instagram_reels</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; instagram_stories</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -24100,34 +23365,36 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>43576.74556856188</v>
+        <v>758.5893812709031</v>
       </c>
       <c r="D21" t="n">
-        <v>517</v>
+        <v>5</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>151.7178762541806</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.7736943907156674</v>
+        <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>35996</v>
+        <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>-7580.745568561877</v>
+        <v>-758.5893812709031</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.8260369040952211</v>
+        <v>0</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-17.39630959047788</v>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>10894.18639214047</v>
+        <v>-100</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -24138,7 +23405,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; instagram_stories</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; others</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -24147,13 +23414,13 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>758.5893812709031</v>
+        <v>168.5754180602007</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>168.5754180602007</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -24165,7 +23432,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>-758.5893812709031</v>
+        <v>-168.5754180602007</v>
       </c>
       <c r="J22" s="6" t="n">
         <v>0</v>
@@ -24187,7 +23454,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; others</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; facebook_instream_video</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -24196,13 +23463,13 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>168.5754180602007</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -24213,14 +23480,18 @@
       <c r="H23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="7" t="n">
-        <v>-168.5754180602007</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <v>-100</v>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -24236,7 +23507,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; facebook_instream_video</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; facebook_mobile_feed</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -24248,22 +23519,22 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -24282,14 +23553,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; facebook_mobile_feed</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; facebook_mobile_reels</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -24301,22 +23572,22 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.333333333333333</v>
+        <v>4.918032786885246</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>8999</v>
+        <v>26997</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>8999</v>
+        <v>26997</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -24342,7 +23613,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; facebook_mobile_reels</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; facebook_stories</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -24354,22 +23625,22 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>162</v>
+        <v>5</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.851851851851852</v>
+        <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>26997</v>
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -24388,14 +23659,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; facebook_stories</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; instagram_feed</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -24407,22 +23678,22 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0</v>
+        <v>2.272727272727273</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -24441,14 +23712,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; instagram_feed</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; instagram_reels</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -24460,22 +23731,22 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.01010101010101</v>
+        <v>1.282051282051282</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>8999</v>
+        <v>17998</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>8999</v>
+        <v>17998</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -24501,7 +23772,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; instagram_reels</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; instagram_stories</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -24513,22 +23784,22 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>378</v>
+        <v>18</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.5291005291005291</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>17998</v>
+        <v>8999</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>17998</v>
+        <v>8999</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -24554,7 +23825,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; instagram_search</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; others</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -24566,22 +23837,22 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -24600,14 +23871,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; instagram_stories</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; instagram_feed</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -24619,16 +23890,20 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>44</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="4" t="n">
-        <v>2.272727272727273</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H31" s="2" t="n">
         <v>8999</v>
@@ -24660,7 +23935,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; others</t>
+          <t>foremost leads | cbo | 14th august &gt; instagram_stories</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -24672,16 +23947,20 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="4" t="n">
-        <v>33.33333333333333</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H32" s="2" t="n">
         <v>8999</v>
@@ -24713,7 +23992,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; facebook_instream_video</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; facebook_mobile_feed</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -24725,7 +24004,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>0</v>
@@ -24766,7 +24045,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; facebook_mobile_feed</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; facebook_mobile_reels</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -24778,7 +24057,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>0</v>
@@ -24819,7 +24098,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; facebook_mobile_reels</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; instagram_feed</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -24831,7 +24110,7 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>0</v>
@@ -24872,7 +24151,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; instagram_feed</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; instagram_reels</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -24884,22 +24163,22 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -24918,14 +24197,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; instagram_reels</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; instagram_stories</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -24937,7 +24216,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>0</v>
@@ -24978,7 +24257,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; instagram_stories</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; others</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -24990,7 +24269,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>0</v>
@@ -25031,7 +24310,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; facebook_instream_video</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; threads_feed</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -25084,7 +24363,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; facebook_mobile_reels</t>
+          <t>foremostleads-gs-13-09 &gt; facebook_desktop_feed</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -25096,7 +24375,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>0</v>
@@ -25137,7 +24416,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; instagram_feed</t>
+          <t>foremostleads-gs-13-09 &gt; facebook_instream_video</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -25149,16 +24428,20 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
-      <c r="G41" s="4" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H41" s="2" t="n">
         <v>0</v>
@@ -25190,7 +24473,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; instagram_reels</t>
+          <t>foremostleads-gs-13-09 &gt; facebook_mobile_feed</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -25202,7 +24485,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>0</v>
@@ -25243,7 +24526,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; instagram_stories</t>
+          <t>foremostleads-gs-13-09 &gt; facebook_mobile_reels</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -25255,22 +24538,22 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I43" s="5" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -25289,14 +24572,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; facebook_mobile_feed</t>
+          <t>foremostleads-gs-13-09 &gt; facebook_notification</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -25308,16 +24591,20 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>16</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
-      <c r="G44" s="4" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H44" s="2" t="n">
         <v>0</v>
@@ -25349,7 +24636,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; facebook_mobile_reels</t>
+          <t>foremostleads-gs-13-09 &gt; facebook_stories</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -25361,7 +24648,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>0</v>
@@ -25402,7 +24689,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; instagram_feed</t>
+          <t>foremostleads-gs-13-09 &gt; instagram_feed</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -25414,22 +24701,22 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -25448,14 +24735,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; instagram_reels</t>
+          <t>foremostleads-gs-13-09 &gt; instagram_reels</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -25467,22 +24754,22 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>0</v>
+        <v>1.785714285714286</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
+        <v>17998</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>17998</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -25501,14 +24788,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; instagram_stories</t>
+          <t>foremostleads-gs-13-09 &gt; instagram_stories</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -25526,16 +24813,16 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>0</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -25554,14 +24841,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; others</t>
+          <t>{{campaign.name}} &gt; {{placement}}</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -25573,7 +24860,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>0</v>
@@ -25606,589 +24893,6 @@
         </is>
       </c>
       <c r="M49" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; threads_feed</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; facebook_desktop_feed</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; facebook_instream_video</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; facebook_mobile_feed</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" t="n">
-        <v>7</v>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; facebook_mobile_reels</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="n">
-        <v>23</v>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; facebook_notification</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; facebook_stories</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="n">
-        <v>4</v>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; instagram_feed</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="n">
-        <v>24</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="4" t="n">
-        <v>4.166666666666666</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I57" s="5" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; instagram_reels</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="n">
-        <v>149</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>2</v>
-      </c>
-      <c r="G58" s="4" t="n">
-        <v>1.342281879194631</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>17998</v>
-      </c>
-      <c r="I58" s="5" t="n">
-        <v>17998</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; instagram_stories</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" t="n">
-        <v>30</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="4" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I59" s="5" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>{{campaign.name}} &gt; {{placement}}</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" t="n">
-        <v>51</v>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -26291,7 +24995,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3795</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="3">
@@ -26301,7 +25005,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3712</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="4">
@@ -26311,7 +25015,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>83</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
